--- a/data/dividends_info_20260416.xlsx
+++ b/data/dividends_info_20260416.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>34.52999877929688</v>
+        <v>34.95000076293945</v>
       </c>
       <c r="I2" t="n">
-        <v>0.260642928414933</v>
+        <v>0.2575107239924151</v>
       </c>
       <c r="J2" t="n">
         <v>333</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.40000152587891</v>
+        <v>55.34999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.263537871335636</v>
+        <v>1.264679348324255</v>
       </c>
       <c r="J3" t="n">
         <v>312</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.140000343322754</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6564551175737441</v>
+        <v>0.6479481481313648</v>
       </c>
       <c r="J4" t="n">
         <v>242</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>34.54000091552734</v>
+        <v>34.95000076293945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2605674511130102</v>
+        <v>0.2575107239924151</v>
       </c>
       <c r="J6" t="n">
         <v>242</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.089999914169312</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I7" t="n">
-        <v>3.68421067761643</v>
+        <v>3.666666833181238</v>
       </c>
       <c r="J7" t="n">
         <v>221</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6.139999866485596</v>
+        <v>6.070000171661377</v>
       </c>
       <c r="I8" t="n">
-        <v>3.257329061058689</v>
+        <v>3.294892822799697</v>
       </c>
       <c r="J8" t="n">
         <v>214</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.849999904632568</v>
+        <v>5.75</v>
       </c>
       <c r="I9" t="n">
-        <v>1.025641042361154</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="J9" t="n">
         <v>186</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>34.54000091552734</v>
+        <v>34.95000076293945</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2605674511130102</v>
+        <v>0.2575107239924151</v>
       </c>
       <c r="J11" t="n">
         <v>158</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.090000152587891</v>
+        <v>6.190000057220459</v>
       </c>
       <c r="I13" t="n">
-        <v>4.105090209131846</v>
+        <v>4.038772175912698</v>
       </c>
       <c r="J13" t="n">
         <v>102</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.711000442504883</v>
+        <v>9.696000099182129</v>
       </c>
       <c r="I14" t="n">
-        <v>2.677376049351048</v>
+        <v>2.68151812438545</v>
       </c>
       <c r="J14" t="n">
         <v>95</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>16.29999923706055</v>
+        <v>16.39999961853027</v>
       </c>
       <c r="I15" t="n">
-        <v>3.68098176738443</v>
+        <v>3.658536670464694</v>
       </c>
       <c r="J15" t="n">
         <v>95</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>18</v>
+        <v>18.64999961853027</v>
       </c>
       <c r="I17" t="n">
-        <v>2.088888888888889</v>
+        <v>2.016085832122022</v>
       </c>
       <c r="J17" t="n">
         <v>95</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.119999885559082</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I20" t="n">
-        <v>4.009434178699683</v>
+        <v>3.899082449407415</v>
       </c>
       <c r="J20" t="n">
         <v>81</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4.539999961853027</v>
+        <v>4.590000152587891</v>
       </c>
       <c r="I21" t="n">
-        <v>1.541850233219586</v>
+        <v>1.525054415532715</v>
       </c>
       <c r="J21" t="n">
         <v>81</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>35.5</v>
+        <v>35.04999923706055</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4225352112676056</v>
+        <v>0.4279600663768223</v>
       </c>
       <c r="J22" t="n">
         <v>81</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>22.78000068664551</v>
+        <v>22.63999938964844</v>
       </c>
       <c r="I24" t="n">
-        <v>4.170324720652557</v>
+        <v>4.196113187327925</v>
       </c>
       <c r="J24" t="n">
         <v>67</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>25.95000076293945</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7514450646124436</v>
+        <v>0.7442747874871527</v>
       </c>
       <c r="J25" t="n">
         <v>67</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.870000004768372</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="I26" t="n">
-        <v>1.764705877853063</v>
+        <v>1.823204477527402</v>
       </c>
       <c r="J26" t="n">
         <v>67</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.135000228881836</v>
+        <v>5.085000038146973</v>
       </c>
       <c r="I27" t="n">
-        <v>5.647516788195908</v>
+        <v>5.703048138140802</v>
       </c>
       <c r="J27" t="n">
         <v>67</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.136000156402588</v>
+        <v>4.10200023651123</v>
       </c>
       <c r="I28" t="n">
-        <v>3.868471807292311</v>
+        <v>3.900536098849197</v>
       </c>
       <c r="J28" t="n">
         <v>67</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.579999923706055</v>
+        <v>2.588000059127808</v>
       </c>
       <c r="I29" t="n">
-        <v>5.372093182115575</v>
+        <v>5.355486740085707</v>
       </c>
       <c r="J29" t="n">
         <v>67</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>58.5099983215332</v>
+        <v>57.97999954223633</v>
       </c>
       <c r="I30" t="n">
-        <v>1.076739049859353</v>
+        <v>1.086581588433901</v>
       </c>
       <c r="J30" t="n">
         <v>67</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>18.54999923706055</v>
+        <v>19.20000076293945</v>
       </c>
       <c r="I31" t="n">
-        <v>4.204851924962125</v>
+        <v>4.06249983857076</v>
       </c>
       <c r="J31" t="n">
         <v>67</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>22.29999923706055</v>
+        <v>22.06999969482422</v>
       </c>
       <c r="I32" t="n">
-        <v>3.811659323231627</v>
+        <v>3.851382019725805</v>
       </c>
       <c r="J32" t="n">
         <v>67</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>34.52999877929688</v>
+        <v>34.95000076293945</v>
       </c>
       <c r="I33" t="n">
-        <v>0.260642928414933</v>
+        <v>0.2575107239924151</v>
       </c>
       <c r="J33" t="n">
         <v>67</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6.656000137329102</v>
+        <v>6.639999866485596</v>
       </c>
       <c r="I34" t="n">
-        <v>2.723858116877255</v>
+        <v>2.730421741649192</v>
       </c>
       <c r="J34" t="n">
         <v>67</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8.350000381469727</v>
+        <v>8.369999885559082</v>
       </c>
       <c r="I35" t="n">
-        <v>3.113772312837141</v>
+        <v>3.106332181062307</v>
       </c>
       <c r="J35" t="n">
         <v>67</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10.11499977111816</v>
+        <v>10.18000030517578</v>
       </c>
       <c r="I36" t="n">
-        <v>2.738507229539749</v>
+        <v>2.721021529431251</v>
       </c>
       <c r="J36" t="n">
         <v>67</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.220000028610229</v>
+        <v>1.240000009536743</v>
       </c>
       <c r="I37" t="n">
-        <v>1.106557351099295</v>
+        <v>1.088709669046174</v>
       </c>
       <c r="J37" t="n">
         <v>60</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>4.067999839782715</v>
+        <v>4.208000183105469</v>
       </c>
       <c r="I38" t="n">
-        <v>2.704031571591101</v>
+        <v>2.614068327316966</v>
       </c>
       <c r="J38" t="n">
         <v>60</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>28.10000038146973</v>
+        <v>28.20000076293945</v>
       </c>
       <c r="I40" t="n">
-        <v>3.950177882317677</v>
+        <v>3.936170106274487</v>
       </c>
       <c r="J40" t="n">
         <v>49</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.9010000228881836</v>
       </c>
       <c r="I41" t="n">
-        <v>3.333333421636513</v>
+        <v>3.329633655705586</v>
       </c>
       <c r="J41" t="n">
         <v>46</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.5370000004768372</v>
+        <v>0.5379999876022339</v>
       </c>
       <c r="I42" t="n">
-        <v>4.283053999921193</v>
+        <v>4.275093035318966</v>
       </c>
       <c r="J42" t="n">
         <v>46</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>18.79999923706055</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="I43" t="n">
-        <v>3.191489491218789</v>
+        <v>3.174603238678043</v>
       </c>
       <c r="J43" t="n">
         <v>46</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.704999923706055</v>
+        <v>2.694999933242798</v>
       </c>
       <c r="I44" t="n">
-        <v>6.654343995447748</v>
+        <v>6.679035415908614</v>
       </c>
       <c r="J44" t="n">
         <v>39</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>8.649999618530273</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="I45" t="n">
-        <v>3.468208245435428</v>
+        <v>3.448275937667407</v>
       </c>
       <c r="J45" t="n">
         <v>39</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>13.17000007629395</v>
+        <v>13.11999988555908</v>
       </c>
       <c r="I46" t="n">
-        <v>1.89825359568525</v>
+        <v>1.905487821498916</v>
       </c>
       <c r="J46" t="n">
         <v>39</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3.400000095367432</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8823529164271378</v>
+        <v>0.8875739344453326</v>
       </c>
       <c r="J47" t="n">
         <v>39</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>13.19999980926514</v>
+        <v>13</v>
       </c>
       <c r="I49" t="n">
-        <v>4.393939457430109</v>
+        <v>4.461538461538462</v>
       </c>
       <c r="J49" t="n">
         <v>39</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.457000017166138</v>
+        <v>2.418999910354614</v>
       </c>
       <c r="I50" t="n">
-        <v>4.232804203231217</v>
+        <v>4.299297389587504</v>
       </c>
       <c r="J50" t="n">
         <v>32</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>9.460000038146973</v>
+        <v>9.928000450134277</v>
       </c>
       <c r="I51" t="n">
-        <v>3.065539099689108</v>
+        <v>2.921031293829945</v>
       </c>
       <c r="J51" t="n">
         <v>32</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.089999914169312</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I52" t="n">
-        <v>3.68421067761643</v>
+        <v>3.666666833181238</v>
       </c>
       <c r="J52" t="n">
         <v>32</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>37.29000091552734</v>
+        <v>36.86999893188477</v>
       </c>
       <c r="I53" t="n">
-        <v>4.397961812109028</v>
+        <v>4.44806088285982</v>
       </c>
       <c r="J53" t="n">
         <v>32</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>36.25</v>
+        <v>36.09999847412109</v>
       </c>
       <c r="I54" t="n">
-        <v>5.517241379310345</v>
+        <v>5.540166439158535</v>
       </c>
       <c r="J54" t="n">
         <v>32</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>4.01200008392334</v>
+        <v>4.027999877929688</v>
       </c>
       <c r="I55" t="n">
-        <v>2.49252238056311</v>
+        <v>2.482621723697719</v>
       </c>
       <c r="J55" t="n">
         <v>32</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>36.56000137329102</v>
+        <v>36.5099983215332</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4060721948124918</v>
+        <v>0.406628339701785</v>
       </c>
       <c r="J56" t="n">
         <v>32</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>22.97999954223633</v>
+        <v>22.71999931335449</v>
       </c>
       <c r="I57" t="n">
-        <v>4.003481367826298</v>
+        <v>4.049295897026005</v>
       </c>
       <c r="J57" t="n">
         <v>32</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>8.335000038146973</v>
+        <v>8.305000305175781</v>
       </c>
       <c r="I58" t="n">
-        <v>3.599280127498303</v>
+        <v>3.612281625240112</v>
       </c>
       <c r="J58" t="n">
         <v>32</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>84.41999816894531</v>
+        <v>84.23999786376953</v>
       </c>
       <c r="I59" t="n">
-        <v>1.231935587014232</v>
+        <v>1.234567932541805</v>
       </c>
       <c r="J59" t="n">
         <v>32</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>48.06999969482422</v>
+        <v>47.91999816894531</v>
       </c>
       <c r="I60" t="n">
-        <v>1.456209703440814</v>
+        <v>1.460768002394535</v>
       </c>
       <c r="J60" t="n">
         <v>32</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>55.40000152587891</v>
+        <v>55.34999847412109</v>
       </c>
       <c r="I61" t="n">
-        <v>3.971119024197713</v>
+        <v>3.974706523304803</v>
       </c>
       <c r="J61" t="n">
         <v>32</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>8.897000312805176</v>
+        <v>8.793999671936035</v>
       </c>
       <c r="I62" t="n">
-        <v>9.666179271256501</v>
+        <v>9.779395406898708</v>
       </c>
       <c r="J62" t="n">
         <v>32</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>12.38199996948242</v>
+        <v>12.21199989318848</v>
       </c>
       <c r="I63" t="n">
-        <v>4.522694244711814</v>
+        <v>4.585653495725568</v>
       </c>
       <c r="J63" t="n">
         <v>32</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1.929999947547913</v>
+        <v>1.970000028610229</v>
       </c>
       <c r="I64" t="n">
-        <v>2.07253891642953</v>
+        <v>2.030456823303637</v>
       </c>
       <c r="J64" t="n">
         <v>32</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>9.060000419616699</v>
+        <v>9.039999961853027</v>
       </c>
       <c r="I65" t="n">
-        <v>3.311258124783752</v>
+        <v>3.318584084800214</v>
       </c>
       <c r="J65" t="n">
         <v>32</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2.259999990463257</v>
+        <v>2.269999980926514</v>
       </c>
       <c r="I66" t="n">
-        <v>4.778761082112308</v>
+        <v>4.757709291077578</v>
       </c>
       <c r="J66" t="n">
         <v>32</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>73.59999847412109</v>
+        <v>74</v>
       </c>
       <c r="I67" t="n">
-        <v>2.798913101505468</v>
+        <v>2.783783783783784</v>
       </c>
       <c r="J67" t="n">
         <v>32</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>15.57999992370605</v>
+        <v>15.51000022888184</v>
       </c>
       <c r="I68" t="n">
-        <v>4.813863951686051</v>
+        <v>4.835589870613882</v>
       </c>
       <c r="J68" t="n">
         <v>32</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>16.28000068664551</v>
+        <v>16.07999992370605</v>
       </c>
       <c r="I69" t="n">
-        <v>1.842751765029655</v>
+        <v>1.865671650643001</v>
       </c>
       <c r="J69" t="n">
         <v>32</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>45.90000152587891</v>
+        <v>46.29999923706055</v>
       </c>
       <c r="I70" t="n">
-        <v>1.851851790289726</v>
+        <v>1.835853162000968</v>
       </c>
       <c r="J70" t="n">
         <v>32</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>33.77999877929688</v>
+        <v>33.86000061035156</v>
       </c>
       <c r="I71" t="n">
-        <v>2.516281914494766</v>
+        <v>2.510336635198231</v>
       </c>
       <c r="J71" t="n">
         <v>32</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>62.68000030517578</v>
+        <v>62.09999847412109</v>
       </c>
       <c r="I72" t="n">
-        <v>2.074026792709911</v>
+        <v>2.093397797009204</v>
       </c>
       <c r="J72" t="n">
         <v>32</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>7.940000057220459</v>
+        <v>8.020000457763672</v>
       </c>
       <c r="I73" t="n">
-        <v>7.556675008514306</v>
+        <v>7.481296331089067</v>
       </c>
       <c r="J73" t="n">
         <v>32</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>6</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I74" t="n">
-        <v>7.833333333333332</v>
+        <v>7.966101566151415</v>
       </c>
       <c r="J74" t="n">
         <v>32</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>6.139999866485596</v>
+        <v>6.070000171661377</v>
       </c>
       <c r="I75" t="n">
-        <v>3.257329061058689</v>
+        <v>3.294892822799697</v>
       </c>
       <c r="J75" t="n">
         <v>32</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>21.78000068664551</v>
+        <v>21.65999984741211</v>
       </c>
       <c r="I76" t="n">
-        <v>4.591368082982449</v>
+        <v>4.616805203345733</v>
       </c>
       <c r="J76" t="n">
         <v>32</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>4.679999828338623</v>
+        <v>4.619999885559082</v>
       </c>
       <c r="I77" t="n">
-        <v>4.594017262524643</v>
+        <v>4.653679768954845</v>
       </c>
       <c r="J77" t="n">
         <v>32</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>22.9950008392334</v>
+        <v>23.40500068664551</v>
       </c>
       <c r="I78" t="n">
-        <v>1.174168254603122</v>
+        <v>1.1535996243489</v>
       </c>
       <c r="J78" t="n">
         <v>32</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>8</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I79" t="n">
-        <v>2.5</v>
+        <v>2.469135686185122</v>
       </c>
       <c r="J79" t="n">
         <v>32</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>9.585000038146973</v>
+        <v>9.505000114440918</v>
       </c>
       <c r="I80" t="n">
-        <v>2.503912353102068</v>
+        <v>2.524986818625796</v>
       </c>
       <c r="J80" t="n">
         <v>32</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>21.65999984741211</v>
+        <v>21.59000015258789</v>
       </c>
       <c r="I81" t="n">
-        <v>3.647276110643129</v>
+        <v>3.659101409989136</v>
       </c>
       <c r="J81" t="n">
         <v>32</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>4.639999866485596</v>
+        <v>4.670000076293945</v>
       </c>
       <c r="I82" t="n">
-        <v>2.004310402500929</v>
+        <v>1.99143465697336</v>
       </c>
       <c r="J82" t="n">
         <v>32</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>5.849999904632568</v>
+        <v>5.75</v>
       </c>
       <c r="I83" t="n">
-        <v>1.025641042361154</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="J83" t="n">
         <v>32</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>37.65999984741211</v>
+        <v>37.36000061035156</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9293680335053188</v>
+        <v>0.9368308198127367</v>
       </c>
       <c r="J84" t="n">
         <v>32</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>7.175000190734863</v>
+        <v>7.304999828338623</v>
       </c>
       <c r="I85" t="n">
-        <v>7.72543533470246</v>
+        <v>7.587953634847169</v>
       </c>
       <c r="J85" t="n">
         <v>32</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>2.099999904632568</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I86" t="n">
-        <v>2.857142986894471</v>
+        <v>2.77777766739881</v>
       </c>
       <c r="J86" t="n">
         <v>32</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>12.5</v>
+        <v>12.75</v>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>1.568627450980392</v>
       </c>
       <c r="J87" t="n">
         <v>32</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>6</v>
+        <v>5.960000038146973</v>
       </c>
       <c r="I88" t="n">
-        <v>1.716666666666667</v>
+        <v>1.728187908401823</v>
       </c>
       <c r="J88" t="n">
         <v>32</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>5.789999961853027</v>
+        <v>5.742000102996826</v>
       </c>
       <c r="I89" t="n">
-        <v>3.281519883450786</v>
+        <v>3.308951525459508</v>
       </c>
       <c r="J89" t="n">
         <v>32</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>10.39999961853027</v>
+        <v>10.25</v>
       </c>
       <c r="I90" t="n">
-        <v>4.153846306208328</v>
+        <v>4.214634146341464</v>
       </c>
       <c r="J90" t="n">
         <v>32</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>27.32999992370605</v>
+        <v>27.17000007629395</v>
       </c>
       <c r="I91" t="n">
-        <v>1.609952437717878</v>
+        <v>1.619433193833163</v>
       </c>
       <c r="J91" t="n">
         <v>32</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.120000004768372</v>
+        <v>1.139999985694885</v>
       </c>
       <c r="I92" t="n">
-        <v>2.678571417167479</v>
+        <v>2.631578980390385</v>
       </c>
       <c r="J92" t="n">
         <v>32</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>54.86000061035156</v>
+        <v>55.22000122070312</v>
       </c>
       <c r="I94" t="n">
-        <v>2.551950390856965</v>
+        <v>2.535313236239319</v>
       </c>
       <c r="J94" t="n">
         <v>32</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>3.638999938964844</v>
+        <v>3.571000099182129</v>
       </c>
       <c r="I95" t="n">
-        <v>8.244023221537578</v>
+        <v>8.401007887642159</v>
       </c>
       <c r="J95" t="n">
         <v>32</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>21.10000038146973</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="I98" t="n">
-        <v>3.317535485045528</v>
+        <v>3.30188667362549</v>
       </c>
       <c r="J98" t="n">
         <v>32</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>2.619999885559082</v>
+        <v>2.559999942779541</v>
       </c>
       <c r="I99" t="n">
-        <v>1.33587792094622</v>
+        <v>1.367187530559023</v>
       </c>
       <c r="J99" t="n">
         <v>32</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.010000228881836</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I100" t="n">
-        <v>5.490848376579791</v>
+        <v>5.454545282583149</v>
       </c>
       <c r="J100" t="n">
         <v>32</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.9769999980926514</v>
+        <v>0.9860000014305115</v>
       </c>
       <c r="I101" t="n">
-        <v>7.164790187989513</v>
+        <v>7.099391470430263</v>
       </c>
       <c r="J101" t="n">
         <v>32</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>50.59999847412109</v>
+        <v>50.15000152587891</v>
       </c>
       <c r="I102" t="n">
-        <v>1.403162097649317</v>
+        <v>1.415752698698561</v>
       </c>
       <c r="J102" t="n">
         <v>32</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>90.30000305175781</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="I103" t="n">
-        <v>1.495016560770449</v>
+        <v>1.477832537000476</v>
       </c>
       <c r="J103" t="n">
         <v>32</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I105" t="n">
-        <v>1.136363636363636</v>
+        <v>1.119402985074627</v>
       </c>
       <c r="J105" t="n">
         <v>32</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>4.131999969482422</v>
+        <v>4.092000007629395</v>
       </c>
       <c r="I106" t="n">
-        <v>4.114230427288565</v>
+        <v>4.154447695088974</v>
       </c>
       <c r="J106" t="n">
         <v>32</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>7.449999809265137</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="I107" t="n">
-        <v>3.986577283272386</v>
+        <v>4.068493044383087</v>
       </c>
       <c r="J107" t="n">
         <v>32</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>57.09999847412109</v>
+        <v>57</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7880910893613235</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="J108" t="n">
         <v>32</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>4.920000076293945</v>
+        <v>4.889999866485596</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8130081174740657</v>
+        <v>0.8179959323546503</v>
       </c>
       <c r="J109" t="n">
         <v>32</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>33.5</v>
+        <v>33.58000183105469</v>
       </c>
       <c r="I110" t="n">
-        <v>3.134328358208956</v>
+        <v>3.126861056418893</v>
       </c>
       <c r="J110" t="n">
         <v>32</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>19.14999961853027</v>
+        <v>19.20000076293945</v>
       </c>
       <c r="I112" t="n">
-        <v>1.98433424318347</v>
+        <v>1.979166588021652</v>
       </c>
       <c r="J112" t="n">
         <v>32</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>24.79999923706055</v>
+        <v>24.94000053405762</v>
       </c>
       <c r="I113" t="n">
-        <v>2.419354913137956</v>
+        <v>2.405773805740905</v>
       </c>
       <c r="J113" t="n">
         <v>32</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>32.90000152587891</v>
+        <v>34.15000152587891</v>
       </c>
       <c r="I114" t="n">
-        <v>1.063829737894366</v>
+        <v>1.02489014454295</v>
       </c>
       <c r="J114" t="n">
         <v>32</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>3.339999914169312</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5089820490078681</v>
+        <v>0.4941860382914094</v>
       </c>
       <c r="J115" t="n">
         <v>32</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>2.775000095367432</v>
+        <v>2.825000047683716</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3603603479759853</v>
+        <v>0.3539822949100208</v>
       </c>
       <c r="J116" t="n">
         <v>32</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>22.18000030517578</v>
+        <v>22.26000022888184</v>
       </c>
       <c r="I117" t="n">
-        <v>5.049594159557537</v>
+        <v>5.03144648914615</v>
       </c>
       <c r="J117" t="n">
         <v>32</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1.480000019073486</v>
+        <v>1.509999990463257</v>
       </c>
       <c r="I118" t="n">
-        <v>6.756756669679118</v>
+        <v>6.622516598117379</v>
       </c>
       <c r="J118" t="n">
         <v>32</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>2.640000104904175</v>
+        <v>2.621999979019165</v>
       </c>
       <c r="I119" t="n">
-        <v>9.848484457141236</v>
+        <v>9.916094663633848</v>
       </c>
       <c r="J119" t="n">
         <v>32</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>2.276000022888184</v>
+        <v>2.355999946594238</v>
       </c>
       <c r="I120" t="n">
-        <v>4.05536024041308</v>
+        <v>3.917657134645782</v>
       </c>
       <c r="J120" t="n">
         <v>32</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>9.199999809265137</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I121" t="n">
-        <v>3.804347904958889</v>
+        <v>3.863134478914378</v>
       </c>
       <c r="J121" t="n">
         <v>25</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>4.860000133514404</v>
+        <v>5</v>
       </c>
       <c r="I122" t="n">
-        <v>1.975308587709434</v>
+        <v>1.92</v>
       </c>
       <c r="J122" t="n">
         <v>25</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>11.80000019073486</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I124" t="n">
-        <v>1.694915226840727</v>
+        <v>1.70940173726859</v>
       </c>
       <c r="J124" t="n">
         <v>25</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>9.140000343322754</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6564551175737441</v>
+        <v>0.6479481481313648</v>
       </c>
       <c r="J125" t="n">
         <v>25</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>2.200000047683716</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I126" t="n">
-        <v>2.727272668160684</v>
+        <v>2.678571417167479</v>
       </c>
       <c r="J126" t="n">
         <v>25</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>16.20000076293945</v>
+        <v>16.29999923706055</v>
       </c>
       <c r="I127" t="n">
-        <v>3.086419607731402</v>
+        <v>3.067484806153692</v>
       </c>
       <c r="J127" t="n">
         <v>25</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>2.730000019073486</v>
+        <v>2.720000028610229</v>
       </c>
       <c r="I129" t="n">
-        <v>4.029304001152793</v>
+        <v>4.044117604520907</v>
       </c>
       <c r="J129" t="n">
         <v>25</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>4.670000076293945</v>
+        <v>4.650000095367432</v>
       </c>
       <c r="I131" t="n">
-        <v>2.034261208736228</v>
+        <v>2.04301071078781</v>
       </c>
       <c r="J131" t="n">
         <v>25</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>1.370000004768372</v>
+        <v>1.340000033378601</v>
       </c>
       <c r="I132" t="n">
-        <v>2.189781014276139</v>
+        <v>2.238805914381933</v>
       </c>
       <c r="J132" t="n">
         <v>25</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>7.800000190734863</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I134" t="n">
-        <v>1.282051250701042</v>
+        <v>1.234567843092561</v>
       </c>
       <c r="J134" t="n">
         <v>25</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>3.410000085830688</v>
+        <v>3.430000066757202</v>
       </c>
       <c r="I136" t="n">
-        <v>4.692081993335886</v>
+        <v>4.664722941281676</v>
       </c>
       <c r="J136" t="n">
         <v>18</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>23.45000076293945</v>
+        <v>23.35000038146973</v>
       </c>
       <c r="I137" t="n">
-        <v>2.601279233065307</v>
+        <v>2.612419657534946</v>
       </c>
       <c r="J137" t="n">
         <v>18</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>12.64999961853027</v>
+        <v>12.55000019073486</v>
       </c>
       <c r="I139" t="n">
-        <v>5.533597004814208</v>
+        <v>5.577689158258185</v>
       </c>
       <c r="J139" t="n">
         <v>18</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>9.310000419616699</v>
+        <v>9.210000038146973</v>
       </c>
       <c r="I140" t="n">
-        <v>5.483350988087471</v>
+        <v>5.542888142079868</v>
       </c>
       <c r="J140" t="n">
         <v>18</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>7.644999980926514</v>
+        <v>7.659999847412109</v>
       </c>
       <c r="I141" t="n">
-        <v>3.531720087293946</v>
+        <v>3.524804247760111</v>
       </c>
       <c r="J141" t="n">
         <v>18</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>5.704999923706055</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I142" t="n">
-        <v>6.134969407197373</v>
+        <v>6.034482560174792</v>
       </c>
       <c r="J142" t="n">
         <v>18</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>18.75</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I144" t="n">
-        <v>4</v>
+        <v>3.989361864023487</v>
       </c>
       <c r="J144" t="n">
         <v>18</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>10.55000019073486</v>
+        <v>10.44999980926514</v>
       </c>
       <c r="I145" t="n">
-        <v>4.075829310198792</v>
+        <v>4.114832610989668</v>
       </c>
       <c r="J145" t="n">
         <v>18</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>4.335000038146973</v>
+        <v>4.304999828338623</v>
       </c>
       <c r="I146" t="n">
-        <v>3.46020758200774</v>
+        <v>3.484320696428174</v>
       </c>
       <c r="J146" t="n">
         <v>18</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>12.07999992370605</v>
+        <v>12.14000034332275</v>
       </c>
       <c r="I147" t="n">
-        <v>1.632193718917756</v>
+        <v>1.624126807446484</v>
       </c>
       <c r="J147" t="n">
         <v>18</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>29.35000038146973</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="I148" t="n">
-        <v>3.747870479396963</v>
+        <v>3.75426630936102</v>
       </c>
       <c r="J148" t="n">
         <v>18</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>46.09999847412109</v>
+        <v>46.04999923706055</v>
       </c>
       <c r="I149" t="n">
-        <v>1.019522810318185</v>
+        <v>1.020629767180862</v>
       </c>
       <c r="J149" t="n">
         <v>18</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>81.09999847412109</v>
+        <v>81.69999694824219</v>
       </c>
       <c r="I150" t="n">
-        <v>1.479654775065031</v>
+        <v>1.46878830455797</v>
       </c>
       <c r="J150" t="n">
         <v>18</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>23.45000076293945</v>
+        <v>23.14999961853027</v>
       </c>
       <c r="I151" t="n">
-        <v>1.1513858900453</v>
+        <v>1.166306714682968</v>
       </c>
       <c r="J151" t="n">
         <v>18</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>10.44999980926514</v>
+        <v>10.5</v>
       </c>
       <c r="I152" t="n">
-        <v>3.636363702735056</v>
+        <v>3.619047619047619</v>
       </c>
       <c r="J152" t="n">
         <v>18</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>28.45000076293945</v>
+        <v>29.64999961853027</v>
       </c>
       <c r="I153" t="n">
-        <v>1.05448151829506</v>
+        <v>1.011804397503297</v>
       </c>
       <c r="J153" t="n">
         <v>18</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>0.1956000030040741</v>
+        <v>0.2000000029802322</v>
       </c>
       <c r="I154" t="n">
-        <v>3.5787320513764</v>
+        <v>3.499999947845937</v>
       </c>
       <c r="J154" t="n">
         <v>11</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>7.550000190734863</v>
+        <v>7.5</v>
       </c>
       <c r="I155" t="n">
-        <v>2.119205244475984</v>
+        <v>2.133333333333333</v>
       </c>
       <c r="J155" t="n">
         <v>11</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>2.190000057220459</v>
+        <v>2.25</v>
       </c>
       <c r="I156" t="n">
-        <v>2.968036452131321</v>
+        <v>2.888888888888889</v>
       </c>
       <c r="J156" t="n">
         <v>11</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>8.189999580383301</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="I157" t="n">
-        <v>3.052503208898818</v>
+        <v>3.101736811223256</v>
       </c>
       <c r="J157" t="n">
         <v>11</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>1.470000028610229</v>
+        <v>1.450000047683716</v>
       </c>
       <c r="I158" t="n">
-        <v>4.761904669225045</v>
+        <v>4.827586048139834</v>
       </c>
       <c r="J158" t="n">
         <v>11</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>6.980000019073486</v>
+        <v>6.920000076293945</v>
       </c>
       <c r="I159" t="n">
-        <v>7.163323762660522</v>
+        <v>7.22543344635017</v>
       </c>
       <c r="J159" t="n">
         <v>4</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>19.10499954223633</v>
+        <v>18.82500076293945</v>
       </c>
       <c r="I160" t="n">
-        <v>3.402250801226214</v>
+        <v>3.452855105746646</v>
       </c>
       <c r="J160" t="n">
         <v>4</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>13.49499988555908</v>
+        <v>13.05000019073486</v>
       </c>
       <c r="I161" t="n">
-        <v>4.001482064315175</v>
+        <v>4.137930974004008</v>
       </c>
       <c r="J161" t="n">
         <v>4</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>6.564000129699707</v>
+        <v>6.572000026702881</v>
       </c>
       <c r="I162" t="n">
-        <v>1.523461273980427</v>
+        <v>1.521606810616055</v>
       </c>
       <c r="J162" t="n">
         <v>4</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>8.979999542236328</v>
+        <v>9</v>
       </c>
       <c r="I163" t="n">
-        <v>1.781737284589599</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="J163" t="n">
         <v>4</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>306</v>
+        <v>305.1000061035156</v>
       </c>
       <c r="I164" t="n">
-        <v>1.181372549019608</v>
+        <v>1.184857400092443</v>
       </c>
       <c r="J164" t="n">
         <v>4</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>28.79999923706055</v>
+        <v>30</v>
       </c>
       <c r="I165" t="n">
-        <v>4.722222347318394</v>
+        <v>4.533333333333333</v>
       </c>
       <c r="J165" t="n">
         <v>4</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>15.60000038146973</v>
+        <v>15.13000011444092</v>
       </c>
       <c r="I166" t="n">
-        <v>3.749999908300548</v>
+        <v>3.866490387145756</v>
       </c>
       <c r="J166" t="n">
         <v>4</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>20.03000068664551</v>
+        <v>19.64999961853027</v>
       </c>
       <c r="I167" t="n">
-        <v>3.145281969061721</v>
+        <v>3.206106932469859</v>
       </c>
       <c r="J167" t="n">
         <v>4</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>121.6750030517578</v>
+        <v>121</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7396753461490856</v>
+        <v>0.7438016528925619</v>
       </c>
       <c r="J168" t="n">
         <v>4</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>70</v>
+        <v>69.18000030517578</v>
       </c>
       <c r="I169" t="n">
-        <v>2.458285714285715</v>
+        <v>2.487424100041897</v>
       </c>
       <c r="J169" t="n">
         <v>4</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>27</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="I170" t="n">
-        <v>0.5185185185185186</v>
+        <v>0.5303030379657029</v>
       </c>
       <c r="J170" t="n">
         <v>-3</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1.570000052452087</v>
+        <v>1.559999942779541</v>
       </c>
       <c r="I171" t="n">
-        <v>3.821655923277815</v>
+        <v>3.846153987229934</v>
       </c>
       <c r="J171" t="n">
         <v>-3</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>2.119999885559082</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I172" t="n">
-        <v>1.603773671479873</v>
+        <v>1.574074011525993</v>
       </c>
       <c r="J172" t="n">
         <v>-17</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>22.9950008392334</v>
+        <v>23.40500068664551</v>
       </c>
       <c r="I173" t="n">
-        <v>1.130680541469673</v>
+        <v>1.110873712335978</v>
       </c>
       <c r="J173" t="n">
         <v>-24</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>34.52999877929688</v>
+        <v>34.95000076293945</v>
       </c>
       <c r="I174" t="n">
-        <v>0.260642928414933</v>
+        <v>0.2575107239924151</v>
       </c>
       <c r="J174" t="n">
         <v>-24</v>
@@ -9792,7 +9792,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9877,7 +9877,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9894,7 +9894,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10081,7 +10081,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10166,7 +10166,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10251,7 +10251,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10268,7 +10268,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10285,7 +10285,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10302,7 +10302,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10319,7 +10319,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10336,7 +10336,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10353,7 +10353,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10363,14 +10363,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10380,14 +10380,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10404,7 +10404,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10414,14 +10414,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10431,14 +10431,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10472,7 +10472,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10489,7 +10489,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10499,14 +10499,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10523,7 +10523,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10540,7 +10540,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10550,14 +10550,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10574,7 +10574,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10591,7 +10591,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10608,7 +10608,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10618,14 +10618,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10635,14 +10635,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10659,7 +10659,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10669,14 +10669,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10686,14 +10686,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10703,14 +10703,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10761,7 +10761,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10771,14 +10771,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10795,7 +10795,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10805,14 +10805,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10829,7 +10829,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10846,7 +10846,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10863,7 +10863,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10880,7 +10880,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10890,14 +10890,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10914,7 +10914,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10931,7 +10931,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10948,7 +10948,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10965,7 +10965,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10975,14 +10975,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10999,7 +10999,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11016,7 +11016,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11033,7 +11033,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11050,7 +11050,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11067,7 +11067,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11077,14 +11077,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11101,7 +11101,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11118,7 +11118,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11135,7 +11135,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11152,7 +11152,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11169,7 +11169,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11179,14 +11179,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11203,7 +11203,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11220,7 +11220,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11237,7 +11237,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11271,7 +11271,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11288,7 +11288,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11305,7 +11305,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11322,7 +11322,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11339,7 +11339,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11356,7 +11356,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11366,14 +11366,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11390,7 +11390,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11407,7 +11407,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11424,7 +11424,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11441,7 +11441,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11451,14 +11451,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11468,14 +11468,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11492,7 +11492,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11509,7 +11509,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11543,7 +11543,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11560,7 +11560,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11577,7 +11577,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11594,7 +11594,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11604,14 +11604,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11628,7 +11628,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11645,7 +11645,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11662,7 +11662,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11679,7 +11679,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11689,14 +11689,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11713,7 +11713,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11730,7 +11730,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11747,7 +11747,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11764,7 +11764,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11774,14 +11774,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11798,7 +11798,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11808,14 +11808,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11832,7 +11832,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11849,7 +11849,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11866,7 +11866,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11883,7 +11883,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11900,7 +11900,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11917,7 +11917,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11934,7 +11934,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11951,7 +11951,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11961,14 +11961,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11978,14 +11978,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12002,7 +12002,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12019,7 +12019,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12036,7 +12036,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12053,7 +12053,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12070,7 +12070,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12087,7 +12087,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12104,7 +12104,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12121,7 +12121,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12138,7 +12138,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12155,7 +12155,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12172,7 +12172,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12182,14 +12182,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12206,7 +12206,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12223,7 +12223,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12240,7 +12240,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12257,7 +12257,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12267,14 +12267,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12291,7 +12291,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12301,14 +12301,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12325,7 +12325,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12335,14 +12335,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12352,14 +12352,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12376,7 +12376,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12393,7 +12393,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12410,7 +12410,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12427,7 +12427,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12444,7 +12444,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12461,7 +12461,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12478,7 +12478,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12495,7 +12495,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12505,14 +12505,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12529,7 +12529,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12546,7 +12546,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12556,14 +12556,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12573,14 +12573,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12597,7 +12597,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12614,7 +12614,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12631,7 +12631,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12648,7 +12648,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12665,7 +12665,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12682,7 +12682,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12692,14 +12692,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12709,14 +12709,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12733,7 +12733,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12750,7 +12750,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12760,14 +12760,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12784,7 +12784,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12801,7 +12801,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12818,7 +12818,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12835,7 +12835,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12845,14 +12845,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12869,7 +12869,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12886,7 +12886,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12903,7 +12903,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -12920,7 +12920,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -12937,7 +12937,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -12947,14 +12947,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -12964,14 +12964,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -12981,14 +12981,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13005,7 +13005,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13022,7 +13022,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13039,7 +13039,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13056,7 +13056,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13073,7 +13073,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13090,7 +13090,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13107,7 +13107,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13124,7 +13124,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13134,14 +13134,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13158,7 +13158,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13175,7 +13175,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13185,14 +13185,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13209,7 +13209,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13226,7 +13226,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13243,7 +13243,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13260,7 +13260,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13270,14 +13270,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13287,14 +13287,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13311,7 +13311,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13321,14 +13321,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13345,7 +13345,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13362,7 +13362,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13379,7 +13379,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13396,7 +13396,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13413,7 +13413,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13430,7 +13430,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13447,7 +13447,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13457,14 +13457,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13474,14 +13474,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13498,7 +13498,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13515,7 +13515,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13549,7 +13549,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13559,14 +13559,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13583,7 +13583,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13600,7 +13600,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13617,7 +13617,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13634,7 +13634,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13651,7 +13651,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13668,7 +13668,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13702,7 +13702,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13719,7 +13719,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13736,7 +13736,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13753,7 +13753,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13770,7 +13770,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13787,7 +13787,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13804,7 +13804,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -13821,7 +13821,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13831,14 +13831,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13848,14 +13848,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13889,7 +13889,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -13906,7 +13906,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -13923,7 +13923,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -13940,7 +13940,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -13950,14 +13950,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -13974,7 +13974,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -13991,7 +13991,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14008,7 +14008,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14025,7 +14025,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14035,14 +14035,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14059,7 +14059,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14076,7 +14076,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14093,7 +14093,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14110,7 +14110,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14120,14 +14120,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14144,7 +14144,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14161,7 +14161,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14178,7 +14178,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14195,7 +14195,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14212,7 +14212,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14229,7 +14229,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14246,7 +14246,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14256,14 +14256,14 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14280,7 +14280,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14297,7 +14297,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14307,14 +14307,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14324,14 +14324,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14348,7 +14348,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14365,7 +14365,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14382,7 +14382,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14399,7 +14399,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14416,7 +14416,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14433,7 +14433,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14450,7 +14450,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14460,14 +14460,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14477,14 +14477,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14501,7 +14501,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14518,7 +14518,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14528,14 +14528,14 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14552,7 +14552,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14569,7 +14569,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14586,7 +14586,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14603,7 +14603,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14620,7 +14620,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14630,14 +14630,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14654,7 +14654,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14671,7 +14671,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14688,7 +14688,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14698,14 +14698,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14722,7 +14722,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14739,7 +14739,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14756,7 +14756,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14766,14 +14766,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14790,7 +14790,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14807,7 +14807,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14817,14 +14817,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14841,7 +14841,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14858,7 +14858,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -14875,7 +14875,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14892,7 +14892,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -14909,7 +14909,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -14926,7 +14926,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -14943,7 +14943,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -14953,14 +14953,14 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -14977,7 +14977,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -14994,7 +14994,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -15004,14 +15004,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15028,7 +15028,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15045,7 +15045,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15062,7 +15062,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15079,7 +15079,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15096,7 +15096,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15113,7 +15113,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15123,14 +15123,14 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15164,7 +15164,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15181,7 +15181,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15191,14 +15191,14 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15208,14 +15208,14 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15249,7 +15249,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15266,7 +15266,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15276,14 +15276,14 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -15317,7 +15317,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15327,14 +15327,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15351,7 +15351,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15368,7 +15368,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15378,14 +15378,14 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15395,7 +15395,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -15419,7 +15419,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15436,7 +15436,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15453,7 +15453,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15463,14 +15463,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15504,7 +15504,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15521,7 +15521,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15538,7 +15538,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15555,7 +15555,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15565,14 +15565,14 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15589,7 +15589,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -15623,7 +15623,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15633,14 +15633,14 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15650,14 +15650,14 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15674,7 +15674,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15691,7 +15691,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15701,14 +15701,14 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15718,14 +15718,14 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15742,7 +15742,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -15752,14 +15752,14 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15769,14 +15769,14 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -15786,14 +15786,14 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -15803,14 +15803,14 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -15827,7 +15827,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -15844,7 +15844,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -15854,14 +15854,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -15871,14 +15871,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -15895,7 +15895,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -15912,7 +15912,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -15929,7 +15929,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -15939,14 +15939,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -15963,7 +15963,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -15980,7 +15980,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -15997,7 +15997,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16007,14 +16007,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16024,14 +16024,14 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16048,7 +16048,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16058,14 +16058,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16082,7 +16082,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16092,14 +16092,14 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16116,7 +16116,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16126,14 +16126,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16143,14 +16143,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16167,7 +16167,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16184,7 +16184,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16194,14 +16194,14 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16218,7 +16218,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16235,7 +16235,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16252,7 +16252,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16262,14 +16262,14 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16279,14 +16279,14 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16296,14 +16296,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16313,14 +16313,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16330,14 +16330,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16354,7 +16354,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16364,14 +16364,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16381,14 +16381,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16405,7 +16405,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16422,7 +16422,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16439,7 +16439,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16456,7 +16456,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16473,7 +16473,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16483,14 +16483,14 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16500,14 +16500,14 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16517,14 +16517,14 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16534,14 +16534,14 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16551,14 +16551,14 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -16568,14 +16568,14 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -16585,14 +16585,14 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -16602,14 +16602,14 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -16619,14 +16619,14 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -16636,14 +16636,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16653,14 +16653,14 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16670,14 +16670,14 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16687,14 +16687,14 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16704,14 +16704,14 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -16721,14 +16721,14 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16738,14 +16738,14 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -16755,14 +16755,14 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -16779,7 +16779,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16789,14 +16789,14 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -16813,7 +16813,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -16830,7 +16830,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16840,14 +16840,14 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -16857,14 +16857,14 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -16874,14 +16874,14 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -16891,14 +16891,14 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -16908,14 +16908,14 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -16925,14 +16925,14 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -16942,14 +16942,14 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -16966,7 +16966,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -16976,14 +16976,14 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -16993,14 +16993,14 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -17017,7 +17017,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -17027,14 +17027,14 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -17044,14 +17044,14 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -17061,14 +17061,14 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -17085,7 +17085,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17095,14 +17095,14 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17119,7 +17119,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17129,14 +17129,14 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17146,14 +17146,14 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17170,7 +17170,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17187,7 +17187,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17238,7 +17238,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17248,14 +17248,14 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17265,14 +17265,14 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17282,14 +17282,14 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17299,14 +17299,14 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17316,14 +17316,14 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17333,14 +17333,14 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17357,7 +17357,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -17367,14 +17367,14 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -17391,7 +17391,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -17401,14 +17401,14 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -17459,7 +17459,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -17476,7 +17476,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -17493,7 +17493,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -17510,7 +17510,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -17520,14 +17520,14 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17544,7 +17544,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17561,7 +17561,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17578,7 +17578,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17595,7 +17595,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17605,14 +17605,14 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17629,7 +17629,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17646,7 +17646,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17663,7 +17663,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17680,7 +17680,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17697,7 +17697,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -17714,7 +17714,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17731,7 +17731,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -17741,14 +17741,14 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -17758,14 +17758,14 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -17775,14 +17775,14 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -17792,14 +17792,14 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -17809,14 +17809,14 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -17826,14 +17826,14 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -17843,14 +17843,14 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -17884,7 +17884,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -17894,14 +17894,14 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -17918,7 +17918,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -17935,7 +17935,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -17945,14 +17945,14 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -17969,7 +17969,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -17979,14 +17979,14 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -17996,14 +17996,14 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -18020,7 +18020,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -18030,14 +18030,14 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -18047,14 +18047,14 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -18071,7 +18071,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -18088,7 +18088,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -18098,14 +18098,14 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -18115,14 +18115,14 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18139,7 +18139,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -18156,7 +18156,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -18173,7 +18173,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -18183,14 +18183,14 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -18207,7 +18207,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -18217,14 +18217,14 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -18241,7 +18241,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -18258,7 +18258,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -18275,7 +18275,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -18285,14 +18285,14 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -18309,7 +18309,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18319,14 +18319,14 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18336,14 +18336,14 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -18353,14 +18353,14 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -18370,14 +18370,14 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -18387,14 +18387,14 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -18411,7 +18411,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -18421,14 +18421,14 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -18438,14 +18438,14 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -18462,7 +18462,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -18472,14 +18472,14 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -18496,7 +18496,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -18513,7 +18513,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -18523,14 +18523,14 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -18540,14 +18540,14 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -18564,7 +18564,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -18598,7 +18598,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -18615,7 +18615,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -18632,7 +18632,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -18642,14 +18642,14 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -18659,14 +18659,14 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -18676,14 +18676,14 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -18693,14 +18693,14 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -18710,14 +18710,14 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -18727,14 +18727,14 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -18751,7 +18751,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -18768,7 +18768,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -18785,7 +18785,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -18802,7 +18802,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -18819,7 +18819,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -18836,7 +18836,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -18853,7 +18853,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -18870,7 +18870,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -18887,7 +18887,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -18897,14 +18897,14 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -18921,7 +18921,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -18938,7 +18938,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -18948,14 +18948,14 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -18972,7 +18972,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -18989,7 +18989,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -19006,7 +19006,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -19016,14 +19016,14 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -19040,7 +19040,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -19050,14 +19050,14 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -19074,7 +19074,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -19091,7 +19091,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -19101,14 +19101,14 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -19125,7 +19125,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -19142,7 +19142,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -19159,7 +19159,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -19169,14 +19169,14 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -19186,14 +19186,14 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -19210,7 +19210,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -19220,14 +19220,14 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -19244,7 +19244,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -19254,14 +19254,14 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -19278,7 +19278,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -19295,7 +19295,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -19312,7 +19312,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -19322,14 +19322,14 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -19339,14 +19339,14 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -19356,14 +19356,14 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -19380,7 +19380,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -19390,14 +19390,14 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -19407,14 +19407,14 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -19424,14 +19424,14 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -19441,14 +19441,14 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -19458,7 +19458,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -19482,7 +19482,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -19499,7 +19499,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -19526,14 +19526,14 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -19543,14 +19543,14 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -19567,7 +19567,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -19577,14 +19577,14 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -19594,14 +19594,14 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -19611,14 +19611,14 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -19635,7 +19635,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -19652,7 +19652,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -19662,14 +19662,14 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -19686,7 +19686,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -19703,7 +19703,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -19720,7 +19720,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -19730,14 +19730,14 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -19747,14 +19747,14 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -19764,14 +19764,14 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -19781,14 +19781,14 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -19805,7 +19805,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -19815,14 +19815,14 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -19847,104 +19847,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BASTOGI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0004412497</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-06-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1.220000028610229</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0135</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1.106557351099295</v>
-      </c>
-      <c r="I2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19955,78 +19860,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ErreDue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Haiki+ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>INNOVATEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>